--- a/salesforce_forms/007_trip_evaluation_form--salesforce_forms.xlsx
+++ b/salesforce_forms/007_trip_evaluation_form--salesforce_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -515,23 +515,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>trip_services</t>
+          <t>trip_evaluation_form_trip_evaluation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Trip Services</t>
+          <t>Trip Evaluation</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>trip_dates</t>
+          <t>trip_evaluation_form_trip_dates</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>trip_location</t>
+          <t>trip_evaluation_form_trip_location</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -577,30 +577,30 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>trip_evaluation_form_trip_type</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Trip Type</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,25 +612,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>evaluation</t>
+          <t>trip_evaluation_form_trip_status</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Evaluation</t>
+          <t>Trip Status</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -646,53 +646,53 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>trip_evaluation_form_organisation_id</t>
+          <t>trip_evaluation_form_project_id</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Trip Evaluation Form Organisation ID</t>
+          <t>Trip Evaluation Form Project ID</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>trip_evaluation_form_organisation_id</t>
+          <t>trip_evaluation_form_project</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Trip Evaluation Form Organisation ID</t>
+          <t>Trip Evaluation Form Project</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,18 +704,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>trip_evaluation_form_organisation</t>
+          <t>trip_evaluation_form_trip_name</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Trip Evaluation Form Organisation</t>
+          <t>Trip Evaluation Form Trip Name</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,18 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>trip_evaluation_form_project</t>
+          <t>trip_evaluation_form_trip</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Trip Evaluation Form Project</t>
+          <t>Trip Evaluation Form Trip</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,18 +750,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>trip_evaluation_form_trip_id</t>
+          <t>trip_evaluation_form_notes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Trip Evaluation Form Trip ID</t>
+          <t>Trip Evaluation Form Notes</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,64 +773,64 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>trip_evaluation_form_trip_name</t>
+          <t>trip_evaluation_form_org_id</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Trip Evaluation Form Trip Name</t>
+          <t>Trip Evaluation Form Organisation ID</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>trip_evaluation_form_trip_type</t>
+          <t>trip_evaluation_form_project_org_id</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Trip Evaluation Form Trip Type</t>
+          <t>Trip Evaluation Form Project Organisation ID</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>trip_evaluation_form_trip_status</t>
+          <t>trip_evaluation_form_project_organisation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Trip Evaluation Form Trip Status</t>
+          <t>Trip Evaluation Form Project Organisation</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,18 +842,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>trip_evaluation_form_client</t>
+          <t>trip_evaluation_form_trip_name_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Trip Evaluation Form Client</t>
+          <t>Trip Evaluation Form Trip Name 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,18 +865,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>trip_evaluation_form_project_organisation_id</t>
+          <t>trip_evaluation_form_trip_type_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Trip Evaluation Form Project Organisation ID</t>
+          <t>Trip Evaluation Form Trip Type</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -888,18 +888,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>trip_evaluation_form_trip_id</t>
+          <t>trip_evaluation_form_trip_status_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Trip Evaluation Form Trip ID</t>
+          <t>Trip Evaluation Form Trip Status</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -911,18 +911,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>trip_evaluation_form_trip</t>
+          <t>trip_evaluation_form_client</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Trip Evaluation Form Trip</t>
+          <t>Trip Evaluation Form Client</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -934,156 +934,18 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>trip_evaluation_form_organisation</t>
+          <t>trip_evaluation_form_project_org</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Trip Evaluation Form Organisation</t>
+          <t>Trip Evaluation Form Project Org</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>trip_evaluation_form_project</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Trip Evaluation Form Project</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>trip_evaluation_form_trip_name</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Trip Evaluation Form Trip Name</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>trip_evaluation_form_trip_type</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Trip Evaluation Form Trip Type</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>trip_evaluation_form_trip_status</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Trip Evaluation Form Trip Status</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>trip_evaluation_form_client_id</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Trip Evaluation Form Client ID</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>trip_evaluation_form_organisation_id</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Trip Evaluation Form Organisation ID</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +960,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,7 +988,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>evaluation_choices</t>
+          <t>trip_evaluation_form_trip_evaluation_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +1005,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>evaluation_choices</t>
+          <t>trip_evaluation_form_trip_evaluation_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,170 +1022,68 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>trip_evaluation_form_client_id_choices</t>
+          <t>trip_evaluation_form_trip_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'salesforce-forms-trip_evaluation_form_client__select_1',_'label':_'client_1'}</t>
+          <t>type_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 'salesforce-forms-trip_evaluation_form_client__select_1', 'label': 'Client 1'}</t>
+          <t>Type 1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>trip_evaluation_form_client_id_choices</t>
+          <t>trip_evaluation_form_trip_type_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'salesforce-forms-trip_evaluation_form_client__select_2',_'label':_'client_2'}</t>
+          <t>type_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 'salesforce-forms-trip_evaluation_form_client__select_2', 'label': 'Client 2'}</t>
+          <t>Type 2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>trip_evaluation_form_organisation_id_choices</t>
+          <t>trip_evaluation_form_trip_status_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>status_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Status 1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>trip_evaluation_form_organisation_id_choices</t>
+          <t>trip_evaluation_form_trip_status_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>status_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>trip_evaluation_form_organisation_id_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>trip_evaluation_form_organisation_id_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>trip_evaluation_form_trip_type_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'id':_'salesforce-forms-trip_evaluation_form_trip_type__select_1',_'label':_'type_1'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'id': 'salesforce-forms-trip_evaluation_form_trip_type__select_1', 'label': 'Type 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>trip_evaluation_form_trip_type_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>{'id':_'salesforce-forms-trip_evaluation_form_trip_type__select_2',_'label':_'type_2'}</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{'id': 'salesforce-forms-trip_evaluation_form_trip_type__select_2', 'label': 'Type 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>trip_evaluation_form_trip_status_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'id':_'salesforce-forms-trip_evaluation_form_trip_status__select_1',_'label':_'status_1'}</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{'id': 'salesforce-forms-trip_evaluation_form_trip_status__select_1', 'label': 'Status 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>trip_evaluation_form_trip_status_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'id':_'salesforce-forms-trip_evaluation_form_trip_status__select_2',_'label':_'status_2'}</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{'id': 'salesforce-forms-trip_evaluation_form_trip_status__select_2', 'label': 'Status 2'}</t>
+          <t>Status 2</t>
         </is>
       </c>
     </row>
